--- a/AAAGameData/DataTables/CatTable.xlsx
+++ b/AAAGameData/DataTables/CatTable.xlsx
@@ -71,7 +71,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>请添加字段, 字段名首字母大写</t>
+    <t>小猫实体预制体</t>
   </si>
   <si>
     <t>小猫0</t>
@@ -1328,7 +1328,7 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/CatTable.xlsx
+++ b/AAAGameData/DataTables/CatTable.xlsx
@@ -1276,7 +1276,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="30.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="12.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="16.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">

--- a/AAAGameData/DataTables/CatTable.xlsx
+++ b/AAAGameData/DataTables/CatTable.xlsx
@@ -77,7 +77,7 @@
     <t>小猫0</t>
   </si>
   <si>
-    <t>CatEntity</t>
+    <t>SmallCatEntity</t>
   </si>
   <si>
     <t>UI/Cats/cat0.png</t>
